--- a/NAN 辦公室到會MENU.xlsx
+++ b/NAN 辦公室到會MENU.xlsx
@@ -1196,9 +1196,6 @@
       <c r="T2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="V2" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
